--- a/input_user.xlsx
+++ b/input_user.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SWAP\swap_wofost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4DE83B-9EA8-4AFF-BBBC-79DEB5E4AF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF930C2E-654C-45AF-8225-5B4EE3A56769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,10 +1013,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="6">
-        <v>51.198633000000001</v>
+        <v>51.139794000000002</v>
       </c>
       <c r="C2" s="6">
-        <v>4.9204559999999997</v>
+        <v>2.814406</v>
       </c>
       <c r="D2" s="7">
         <v>42370</v>
